--- a/sensitivity_analysis/gamma_sensitivity/model_sensitivity/graphs/SS_Comparison_Gamma_val.xlsx
+++ b/sensitivity_analysis/gamma_sensitivity/model_sensitivity/graphs/SS_Comparison_Gamma_val.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="79" uniqueCount="79">
   <si>
     <t>Variable</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>xi</t>
-  </si>
-  <si>
-    <t>spread</t>
   </si>
   <si>
     <t>U_H</t>
@@ -298,13 +295,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="15.5703125" customWidth="true"/>
     <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.5703125" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -313,16 +310,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="D1" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="E1" s="0" t="s">
         <v>78</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2">
@@ -330,16 +327,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>0.14388224519942355</v>
+        <v>0.22044594474004953</v>
       </c>
       <c r="C2" s="0">
-        <v>0.14428960910359803</v>
+        <v>0.22098779215444392</v>
       </c>
       <c r="D2" s="0">
-        <v>0.15236564675841457</v>
+        <v>0.21496525903578595</v>
       </c>
       <c r="E2" s="0">
-        <v>0.15281692989148882</v>
+        <v>0.2155055302374613</v>
       </c>
     </row>
     <row r="3">
@@ -347,16 +344,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>0.32429464325123636</v>
+        <v>0.32141413782875433</v>
       </c>
       <c r="C3" s="0">
-        <v>0.32376524968509607</v>
+        <v>0.32069140954111869</v>
       </c>
       <c r="D3" s="0">
-        <v>0.31968308137907187</v>
+        <v>0.32344350514312059</v>
       </c>
       <c r="E3" s="0">
-        <v>0.31915046304146283</v>
+        <v>0.32271176037110499</v>
       </c>
     </row>
     <row r="4">
@@ -364,16 +361,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>0.046041577048937063</v>
+        <v>0.11337486336832386</v>
       </c>
       <c r="C4" s="0">
-        <v>0.018965932139719761</v>
+        <v>0.033807886794255192</v>
       </c>
       <c r="D4" s="0">
-        <v>0.048756938246151106</v>
+        <v>0.11055615879374737</v>
       </c>
       <c r="E4" s="0">
-        <v>0.020105116021428077</v>
+        <v>0.032969181232925936</v>
       </c>
     </row>
     <row r="5">
@@ -381,16 +378,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>7.2022737342301696e-06</v>
+        <v>3.0912574842893919e-05</v>
       </c>
       <c r="C5" s="0">
-        <v>0.029008268654093793</v>
+        <v>0.092170723816412919</v>
       </c>
       <c r="D5" s="0">
-        <v>7.6261973954749101e-06</v>
+        <v>3.0144032208901665e-05</v>
       </c>
       <c r="E5" s="0">
-        <v>0.03070683124132256</v>
+        <v>0.089884153847487699</v>
       </c>
     </row>
     <row r="6">
@@ -398,16 +395,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>0.046048658269278571</v>
+        <v>0.11340364667618352</v>
       </c>
       <c r="C6" s="0">
-        <v>0.047762013458020468</v>
+        <v>0.12313954699715227</v>
       </c>
       <c r="D6" s="0">
-        <v>0.048764436322720088</v>
+        <v>0.11058422649640919</v>
       </c>
       <c r="E6" s="0">
-        <v>0.05058868398082484</v>
+        <v>0.12008470291551551</v>
       </c>
     </row>
     <row r="7">
@@ -415,16 +412,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>0.40603746672002755</v>
+        <v>0.38778758045286177</v>
       </c>
       <c r="C7" s="0">
-        <v>0.40558179556450591</v>
+        <v>0.38760108113848307</v>
       </c>
       <c r="D7" s="0">
-        <v>0.38576717325387394</v>
+        <v>0.40336251506419357</v>
       </c>
       <c r="E7" s="0">
-        <v>0.38529005265465227</v>
+        <v>0.40313371925533514</v>
       </c>
     </row>
     <row r="8">
@@ -432,16 +429,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>0.33210491294422384</v>
+        <v>0.32060759189760435</v>
       </c>
       <c r="C8" s="0">
-        <v>0.33254650563002836</v>
+        <v>0.32059184182600731</v>
       </c>
       <c r="D8" s="0">
-        <v>0.35513681732160118</v>
+        <v>0.30738357258249421</v>
       </c>
       <c r="E8" s="0">
-        <v>0.35566238510933401</v>
+        <v>0.30739685897909175</v>
       </c>
     </row>
     <row r="9">
@@ -449,16 +446,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>1.6211586731585348</v>
+        <v>1.6725579771688905</v>
       </c>
       <c r="C9" s="0">
-        <v>1.6202330166730439</v>
+        <v>1.6803615600989337</v>
       </c>
       <c r="D9" s="0">
-        <v>1.6023896122482493</v>
+        <v>1.8119408623808682</v>
       </c>
       <c r="E9" s="0">
-        <v>1.5996274485987669</v>
+        <v>1.8205786493125813</v>
       </c>
     </row>
     <row r="10">
@@ -466,16 +463,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>0.86236716120720802</v>
+        <v>3.764021575452098</v>
       </c>
       <c r="C10" s="0">
-        <v>0.85022243459771296</v>
+        <v>3.7525626470097779</v>
       </c>
       <c r="D10" s="0">
-        <v>2.6447608695562761</v>
+        <v>2.0620108558324328</v>
       </c>
       <c r="E10" s="0">
-        <v>2.5367255560810484</v>
+        <v>2.0553632795673566</v>
       </c>
     </row>
     <row r="11">
@@ -483,16 +480,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>11.621472268588802</v>
+        <v>0.46701336213906386</v>
       </c>
       <c r="C11" s="0">
-        <v>11.671597051845797</v>
+        <v>0.46023917018812383</v>
       </c>
       <c r="D11" s="0">
-        <v>14.91507327925391</v>
+        <v>0.3545384169575278</v>
       </c>
       <c r="E11" s="0">
-        <v>14.972600764428774</v>
+        <v>0.34822860329825239</v>
       </c>
     </row>
     <row r="12">
@@ -500,16 +497,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>4.3516382836464587</v>
+        <v>3.3097680913244374</v>
       </c>
       <c r="C12" s="0">
-        <v>4.4062520162904226</v>
+        <v>3.2785537596042653</v>
       </c>
       <c r="D12" s="0">
-        <v>5.4590128773532989</v>
+        <v>2.7522365504765265</v>
       </c>
       <c r="E12" s="0">
-        <v>5.6219805326727421</v>
+        <v>2.7176854027496744</v>
       </c>
     </row>
     <row r="13">
@@ -517,16 +514,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>49.037711338318424</v>
+        <v>14.489057422092559</v>
       </c>
       <c r="C13" s="0">
-        <v>48.244155609512525</v>
+        <v>14.380357534985771</v>
       </c>
       <c r="D13" s="0">
-        <v>154.0903087260784</v>
+        <v>7.6951119091999498</v>
       </c>
       <c r="E13" s="0">
-        <v>147.63432991827182</v>
+        <v>7.6071864428673566</v>
       </c>
     </row>
     <row r="14">
@@ -534,16 +531,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>402.69838355200898</v>
+        <v>32.766084020211444</v>
       </c>
       <c r="C14" s="0">
-        <v>403.09051505301409</v>
+        <v>32.739232580655198</v>
       </c>
       <c r="D14" s="0">
-        <v>426.44146036868483</v>
+        <v>31.951459788924094</v>
       </c>
       <c r="E14" s="0">
-        <v>426.91133974108988</v>
+        <v>31.927038177433495</v>
       </c>
     </row>
     <row r="15">
@@ -551,16 +548,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>10.067459588800224</v>
+        <v>0.81915210050528586</v>
       </c>
       <c r="C15" s="0">
-        <v>10.077262876325353</v>
+        <v>0.81848081451638011</v>
       </c>
       <c r="D15" s="0">
-        <v>10.661036509217176</v>
+        <v>0.79878649472310237</v>
       </c>
       <c r="E15" s="0">
-        <v>10.672783493527248</v>
+        <v>0.79817595443583766</v>
       </c>
     </row>
     <row r="16">
@@ -568,16 +565,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>9.3605973343014917</v>
+        <v>0.77403060902948795</v>
       </c>
       <c r="C16" s="0">
-        <v>9.4212947302050889</v>
+        <v>0.76886942746758069</v>
       </c>
       <c r="D16" s="0">
-        <v>11.488966363805094</v>
+        <v>0.70580750776309675</v>
       </c>
       <c r="E16" s="0">
-        <v>11.614180029971733</v>
+        <v>0.70094771560776103</v>
       </c>
     </row>
     <row r="17">
@@ -585,16 +582,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>0.41332972613047364</v>
+        <v>0.31203934076507589</v>
       </c>
       <c r="C17" s="0">
-        <v>0.41372507354295562</v>
+        <v>0.31155824555142753</v>
       </c>
       <c r="D17" s="0">
-        <v>0.43769962371569054</v>
+        <v>0.30428147723932319</v>
       </c>
       <c r="E17" s="0">
-        <v>0.43817391066712807</v>
+        <v>0.30382911315068994</v>
       </c>
     </row>
     <row r="18">
@@ -619,16 +616,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>0.093605973343014931</v>
+        <v>0.077403060902948809</v>
       </c>
       <c r="C19" s="0">
-        <v>0.094212947302050903</v>
+        <v>0.076886942746758072</v>
       </c>
       <c r="D19" s="0">
-        <v>0.11488966363805093</v>
+        <v>0.070580750776309667</v>
       </c>
       <c r="E19" s="0">
-        <v>0.11614180029971734</v>
+        <v>0.070094771560776106</v>
       </c>
     </row>
     <row r="20">
@@ -636,16 +633,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>0.018416630819574824</v>
+        <v>0.056687431684161932</v>
       </c>
       <c r="C20" s="0">
-        <v>0.007586372855887904</v>
+        <v>0.016903943397127596</v>
       </c>
       <c r="D20" s="0">
-        <v>0.019502775298460447</v>
+        <v>0.055278079396873687</v>
       </c>
       <c r="E20" s="0">
-        <v>0.0080420464085712313</v>
+        <v>0.016484590616462968</v>
       </c>
     </row>
     <row r="21">
@@ -653,16 +650,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>0.50879662511225276</v>
+        <v>1.5056086301808393</v>
       </c>
       <c r="C21" s="0">
-        <v>0.50163123641265062</v>
+        <v>1.5010250588039113</v>
       </c>
       <c r="D21" s="0">
-        <v>1.5604089130382026</v>
+        <v>0.82480434233297317</v>
       </c>
       <c r="E21" s="0">
-        <v>1.4966680780878185</v>
+        <v>0.82214531182694262</v>
       </c>
     </row>
     <row r="22">
@@ -670,16 +667,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>0.49037711338318424</v>
+        <v>1.4489057422092559</v>
       </c>
       <c r="C22" s="0">
-        <v>0.48244155609512523</v>
+        <v>1.4380357534985773</v>
       </c>
       <c r="D22" s="0">
-        <v>1.5409030872607841</v>
+        <v>0.76951119091999498</v>
       </c>
       <c r="E22" s="0">
-        <v>1.4763432991827183</v>
+        <v>0.76071864428673575</v>
       </c>
     </row>
     <row r="23">
@@ -687,16 +684,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>0.51400436468071065</v>
+        <v>0.39396171402600266</v>
       </c>
       <c r="C23" s="0">
-        <v>0.51450488147262663</v>
+        <v>0.39363886680553178</v>
       </c>
       <c r="D23" s="0">
-        <v>0.54431003665057209</v>
+        <v>0.38416711183163849</v>
       </c>
       <c r="E23" s="0">
-        <v>0.54490979085410129</v>
+        <v>0.38387347955271922</v>
       </c>
     </row>
     <row r="24">
@@ -704,16 +701,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>4.02698383552009</v>
+        <v>3.2766084020211443</v>
       </c>
       <c r="C24" s="0">
-        <v>4.030905150530141</v>
+        <v>3.27392325806552</v>
       </c>
       <c r="D24" s="0">
-        <v>4.2644146036868484</v>
+        <v>3.1951459788924099</v>
       </c>
       <c r="E24" s="0">
-        <v>4.2691133974108988</v>
+        <v>3.1927038177433498</v>
       </c>
     </row>
     <row r="25">
@@ -721,16 +718,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>0.10067459588800225</v>
+        <v>0.081915210050528597</v>
       </c>
       <c r="C25" s="0">
-        <v>0.10077262876325353</v>
+        <v>0.081848081451638022</v>
       </c>
       <c r="D25" s="0">
-        <v>0.10661036509217177</v>
+        <v>0.079878649472310242</v>
       </c>
       <c r="E25" s="0">
-        <v>0.10672783493527249</v>
+        <v>0.079817595443583772</v>
       </c>
     </row>
     <row r="26">
@@ -738,16 +735,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>0.18647989092271094</v>
+        <v>0.1387823409522691</v>
       </c>
       <c r="C26" s="0">
-        <v>0.18666147754565615</v>
+        <v>0.13866861037533307</v>
       </c>
       <c r="D26" s="0">
-        <v>0.19747473608670038</v>
+        <v>0.13533196043854132</v>
       </c>
       <c r="E26" s="0">
-        <v>0.19769232587025032</v>
+        <v>0.13522852151644121</v>
       </c>
     </row>
     <row r="27">
@@ -755,16 +752,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
+        <v>0.83333333333333315</v>
+      </c>
+      <c r="C27" s="0">
         <v>0.83333333333333293</v>
       </c>
-      <c r="C27" s="0">
-        <v>0.83333333333333348</v>
-      </c>
       <c r="D27" s="0">
+        <v>0.8333333333333337</v>
+      </c>
+      <c r="E27" s="0">
         <v>0.83333333333333359</v>
-      </c>
-      <c r="E27" s="0">
-        <v>0.83333333333333315</v>
       </c>
     </row>
     <row r="28">
@@ -772,16 +769,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>0.085667394113452047</v>
+        <v>0.06566028567100049</v>
       </c>
       <c r="C28" s="0">
-        <v>0.085750813578770971</v>
+        <v>0.065606477800922144</v>
       </c>
       <c r="D28" s="0">
-        <v>0.090718339441762025</v>
+        <v>0.06402785197193965</v>
       </c>
       <c r="E28" s="0">
-        <v>0.090818298475683734</v>
+        <v>0.063978913258786463</v>
       </c>
     </row>
     <row r="29">
@@ -806,16 +803,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0.0079385792295628768</v>
+        <v>0.01174277523194831</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0084621337232799361</v>
+        <v>0.011280464945835929</v>
       </c>
       <c r="D30" s="0">
-        <v>0.024171324196288924</v>
+        <v>0.0065528988043700243</v>
       </c>
       <c r="E30" s="0">
-        <v>0.0253235018240336</v>
+        <v>0.0061158583019896521</v>
       </c>
     </row>
     <row r="31">
@@ -840,16 +837,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0.041987169852963198</v>
+        <v>4.0182675188718049</v>
       </c>
       <c r="C32" s="0">
-        <v>0.04175760593837876</v>
+        <v>4.1039437027936936</v>
       </c>
       <c r="D32" s="0">
-        <v>0.030580864775151363</v>
+        <v>5.9238493029040482</v>
       </c>
       <c r="E32" s="0">
-        <v>0.030438289629865417</v>
+        <v>6.0809330559543735</v>
       </c>
     </row>
     <row r="33">
@@ -857,16 +854,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0.050384603823555842</v>
+        <v>4.8219210226461664</v>
       </c>
       <c r="C33" s="0">
-        <v>0.050109127126054503</v>
+        <v>4.9247324433524327</v>
       </c>
       <c r="D33" s="0">
-        <v>0.036697037730181632</v>
+        <v>7.1086191634848577</v>
       </c>
       <c r="E33" s="0">
-        <v>0.036525947555838496</v>
+        <v>7.2971196671452478</v>
       </c>
     </row>
     <row r="34">
@@ -874,16 +871,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0.057552898079769425</v>
+        <v>0.066133783422014883</v>
       </c>
       <c r="C34" s="0">
-        <v>0.057715843641439217</v>
+        <v>0.066296337646333178</v>
       </c>
       <c r="D34" s="0">
-        <v>0.060946258703365848</v>
+        <v>0.064489577710735754</v>
       </c>
       <c r="E34" s="0">
-        <v>0.061126771956595508</v>
+        <v>0.064651659071238404</v>
       </c>
     </row>
     <row r="35">
@@ -891,16 +888,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>0</v>
+        <v>0.089359545030377144</v>
       </c>
       <c r="C35" s="0">
-        <v>0</v>
+        <v>0.089286315882192158</v>
       </c>
       <c r="D35" s="0">
-        <v>0</v>
+        <v>0.087137904793061771</v>
       </c>
       <c r="E35" s="0">
-        <v>0</v>
+        <v>0.087071302263129799</v>
       </c>
     </row>
     <row r="36">
@@ -908,16 +905,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>-2.3021159231907768</v>
+        <v>-0.68810709723158303</v>
       </c>
       <c r="C36" s="0">
-        <v>-2.308633745657569</v>
+        <v>-0.68862695176043454</v>
       </c>
       <c r="D36" s="0">
-        <v>-2.4378503481346336</v>
+        <v>-0.67099950772592576</v>
       </c>
       <c r="E36" s="0">
-        <v>-2.4450708782638206</v>
+        <v>-0.67154350440871124</v>
       </c>
     </row>
     <row r="37">
@@ -942,16 +939,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>0.00092371245047243337</v>
+        <v>0.0014326420795254954</v>
       </c>
       <c r="C38" s="0">
-        <v>0.011982626104431912</v>
+        <v>0.046507960493134645</v>
       </c>
       <c r="D38" s="0">
-        <v>0.00097818924388121229</v>
+        <v>0.0013970240010262929</v>
       </c>
       <c r="E38" s="0">
-        <v>0.012684834816957587</v>
+        <v>0.045354191689155422</v>
       </c>
     </row>
     <row r="39">
@@ -959,16 +956,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>0.00092083154097874129</v>
+        <v>0.0014171857921040484</v>
       </c>
       <c r="C39" s="0">
-        <v>0.00037931864279439526</v>
+        <v>0.00042259858492818992</v>
       </c>
       <c r="D39" s="0">
-        <v>0.00097513876492302234</v>
+        <v>0.0013819519849218424</v>
       </c>
       <c r="E39" s="0">
-        <v>0.00040210232042856161</v>
+        <v>0.00041211476541157428</v>
       </c>
     </row>
     <row r="40">
@@ -993,16 +990,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>1.5389636322717943</v>
+        <v>1.5849419709205088</v>
       </c>
       <c r="C41" s="0">
-        <v>1.5389636322717959</v>
+        <v>1.5849419709205081</v>
       </c>
       <c r="D41" s="0">
-        <v>1.5389636322717961</v>
+        <v>1.5849419709205104</v>
       </c>
       <c r="E41" s="0">
-        <v>1.5389636322717948</v>
+        <v>1.5849419709205099</v>
       </c>
     </row>
     <row r="42">
@@ -1010,16 +1007,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>0.2654861339081046</v>
+        <v>0.47904977341267413</v>
       </c>
       <c r="C42" s="0">
-        <v>0.2661791768273557</v>
+        <v>0.47973592639510576</v>
       </c>
       <c r="D42" s="0">
-        <v>0.28519473319130734</v>
+        <v>0.46420877364974172</v>
       </c>
       <c r="E42" s="0">
-        <v>0.28598545350588511</v>
+        <v>0.46490574565379189</v>
       </c>
     </row>
     <row r="43">
@@ -1027,16 +1024,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>1.2888896127006575</v>
+        <v>1.1148774675169169</v>
       </c>
       <c r="C43" s="0">
-        <v>1.2884314822599963</v>
+        <v>1.1140185648348173</v>
       </c>
       <c r="D43" s="0">
-        <v>1.2763649252364091</v>
+        <v>1.133930535674111</v>
       </c>
       <c r="E43" s="0">
-        <v>1.2758831199263565</v>
+        <v>1.1330148595697069</v>
       </c>
     </row>
     <row r="44">
@@ -1044,16 +1041,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>2.1820843175460252</v>
+        <v>3.3126658405253546</v>
       </c>
       <c r="C44" s="0">
-        <v>2.1555022571662303</v>
+        <v>3.2872438346220321</v>
       </c>
       <c r="D44" s="0">
-        <v>2.2568578031473017</v>
+        <v>2.8896288511609165</v>
       </c>
       <c r="E44" s="0">
-        <v>2.1715172384420267</v>
+        <v>2.8666483976873018</v>
       </c>
     </row>
     <row r="45">
@@ -1078,16 +1075,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="C46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="D46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
       <c r="E46" s="0">
-        <v>0.035101010101010167</v>
+        <v>0.033064516129032252</v>
       </c>
     </row>
     <row r="47">
@@ -1095,16 +1092,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>0.0050724432212038029</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="C47" s="0">
-        <v>0.0053350924204853415</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="D47" s="0">
-        <v>0.005073737045047262</v>
+        <v>0.002986042183622827</v>
       </c>
       <c r="E47" s="0">
-        <v>0.0053517698774078254</v>
+        <v>0.002986042183622827</v>
       </c>
     </row>
     <row r="48">
@@ -1112,16 +1109,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>0.025521734698584982</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="C48" s="0">
-        <v>0.026912476870219283</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="D48" s="0">
-        <v>0.025528585568059117</v>
+        <v>0.015677419354838702</v>
       </c>
       <c r="E48" s="0">
-        <v>0.027000784935582361</v>
+        <v>0.015677419354838702</v>
       </c>
     </row>
     <row r="49">
@@ -1129,16 +1126,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="C49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="D49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
       <c r="E49" s="0">
-        <v>0.010101010101010166</v>
+        <v>0.0080645161290322509</v>
       </c>
     </row>
     <row r="50">
@@ -1146,16 +1143,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>0.010147195723533788</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="C50" s="0">
-        <v>0.010700141406231762</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="D50" s="0">
-        <v>0.010149919563204227</v>
+        <v>0.013064516129032252</v>
       </c>
       <c r="E50" s="0">
-        <v>0.010735251841858046</v>
+        <v>0.013064516129032252</v>
       </c>
     </row>
     <row r="51">
@@ -1214,16 +1211,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>0.020267802944246373</v>
+        <v>0.019198383854861931</v>
       </c>
       <c r="C54" s="0">
-        <v>0.015079201532185754</v>
+        <v>0.019212241850615264</v>
       </c>
       <c r="D54" s="0">
-        <v>0.021858342452273131</v>
+        <v>0.018097234336843068</v>
       </c>
       <c r="E54" s="0">
-        <v>0.015927825245990124</v>
+        <v>0.018112642969085515</v>
       </c>
     </row>
     <row r="55">
@@ -1265,16 +1262,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>0.0050285668798063631</v>
+        <v>-4.9389319817457409</v>
       </c>
       <c r="C57" s="0">
-        <v>0.0047659176805248246</v>
+        <v>-4.9285259605580558</v>
       </c>
       <c r="D57" s="0">
-        <v>0.0050272730559629041</v>
+        <v>-5.001496428355761</v>
       </c>
       <c r="E57" s="0">
-        <v>0.0047492402236023407</v>
+        <v>-4.9908208448063407</v>
       </c>
     </row>
     <row r="58">
@@ -1282,16 +1279,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>-5.9968223221241548</v>
+        <v>-164.63106605819189</v>
       </c>
       <c r="C58" s="0">
-        <v>-5.9856287006100573</v>
+        <v>-164.28419868526814</v>
       </c>
       <c r="D58" s="0">
-        <v>-5.82748510015848</v>
+        <v>-166.71654761185846</v>
       </c>
       <c r="E58" s="0">
-        <v>-5.8162245760804909</v>
+        <v>-166.36069482687728</v>
       </c>
     </row>
     <row r="59">
@@ -1299,16 +1296,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>-99.947038702069193</v>
+        <v>0.22044594474004836</v>
       </c>
       <c r="C59" s="0">
-        <v>-99.760478343500793</v>
+        <v>0.22098779215444281</v>
       </c>
       <c r="D59" s="0">
-        <v>-97.124751669307912</v>
+        <v>0.21496525902904906</v>
       </c>
       <c r="E59" s="0">
-        <v>-96.93707626800807</v>
+        <v>0.21550553023218327</v>
       </c>
     </row>
     <row r="60">
@@ -1316,16 +1313,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>0.14388224519928333</v>
+        <v>0.11340577594316675</v>
       </c>
       <c r="C60" s="0">
-        <v>0.14428960910341526</v>
+        <v>0.12597861061066812</v>
       </c>
       <c r="D60" s="0">
-        <v>0.15236564671912473</v>
+        <v>0.11058630282595627</v>
       </c>
       <c r="E60" s="0">
-        <v>0.15281692983296535</v>
+        <v>0.12285333508041363</v>
       </c>
     </row>
     <row r="61">
@@ -1333,16 +1330,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>0.04604877932267129</v>
+        <v>-4.601652410435638</v>
       </c>
       <c r="C61" s="0">
-        <v>0.047974200793813551</v>
+        <v>-4.6005668674852309</v>
       </c>
       <c r="D61" s="0">
-        <v>0.048764564443546578</v>
+        <v>-4.4588732823528208</v>
       </c>
       <c r="E61" s="0">
-        <v>0.050811947262750637</v>
+        <v>-4.4580513406031717</v>
       </c>
     </row>
     <row r="62">
@@ -1350,16 +1347,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>-4.5858347056724709</v>
+        <v>-230.08262052178191</v>
       </c>
       <c r="C62" s="0">
-        <v>-4.5895827148680395</v>
+        <v>-230.02834337426231</v>
       </c>
       <c r="D62" s="0">
-        <v>-4.7667978576850372</v>
+        <v>-222.94366411764082</v>
       </c>
       <c r="E62" s="0">
-        <v>-4.7717142183809553</v>
+        <v>-222.90256703015837</v>
       </c>
     </row>
     <row r="63">
@@ -1367,16 +1364,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>-152.86115685574953</v>
+        <v>0.44679772515187544</v>
       </c>
       <c r="C63" s="0">
-        <v>-152.98609049560156</v>
+        <v>0.44643157941095157</v>
       </c>
       <c r="D63" s="0">
-        <v>-158.89326192283505</v>
+        <v>0.43568952390895138</v>
       </c>
       <c r="E63" s="0">
-        <v>-159.0571406126989</v>
+        <v>0.43535651127149444</v>
       </c>
     </row>
     <row r="64">
@@ -1384,16 +1381,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>0.42804657262066625</v>
+        <v>1.7766041018134713</v>
       </c>
       <c r="C64" s="0">
-        <v>0.42846338716927962</v>
+        <v>1.7711955313613008</v>
       </c>
       <c r="D64" s="0">
-        <v>0.45328417728938175</v>
+        <v>3.1738257367007154</v>
       </c>
       <c r="E64" s="0">
-        <v>0.4537836335537464</v>
+        <v>3.1635955883482669</v>
       </c>
     </row>
     <row r="65">
@@ -1401,16 +1398,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>2.675137755745753</v>
+        <v>-3.4762822685648609</v>
       </c>
       <c r="C65" s="0">
-        <v>2.6421934899762838</v>
+        <v>-3.5003522205237143</v>
       </c>
       <c r="D65" s="0">
-        <v>0.97160463052836432</v>
+        <v>-3.9616874498646597</v>
       </c>
       <c r="E65" s="0">
-        <v>0.93689302363621074</v>
+        <v>-3.9958017173688924</v>
       </c>
     </row>
     <row r="66">
@@ -1418,16 +1415,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>-0.59147121403898451</v>
+        <v>-434.53528357061282</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.59018028664177979</v>
+        <v>-437.54402756546733</v>
       </c>
       <c r="D66" s="0">
-        <v>-0.52214587400447632</v>
+        <v>-495.21093123308378</v>
       </c>
       <c r="E66" s="0">
-        <v>-0.5210875590725198</v>
+        <v>-499.47521467111687</v>
       </c>
     </row>
     <row r="67">
@@ -1435,16 +1432,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>-59.147121403898517</v>
+        <v>1.2861654626443519</v>
       </c>
       <c r="C67" s="0">
-        <v>-59.018028664177812</v>
+        <v>1.2787199847045017</v>
       </c>
       <c r="D67" s="0">
-        <v>-52.214587400447527</v>
+        <v>1.1533249116806283</v>
       </c>
       <c r="E67" s="0">
-        <v>-52.108755907252231</v>
+        <v>1.1464045577340873</v>
       </c>
     </row>
     <row r="68">
@@ -1452,16 +1449,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>21.688931857389026</v>
+        <v>58.219297138495271</v>
       </c>
       <c r="C68" s="0">
-        <v>21.748859928171154</v>
+        <v>57.896995748376973</v>
       </c>
       <c r="D68" s="0">
-        <v>25.57610978847109</v>
+        <v>47.599513839600611</v>
       </c>
       <c r="E68" s="0">
-        <v>25.645384257956024</v>
+        <v>47.324873125511374</v>
       </c>
     </row>
     <row r="69">
@@ -1469,16 +1466,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>461.23173654470526</v>
+        <v>-217.80210959487002</v>
       </c>
       <c r="C69" s="0">
-        <v>460.83235682928387</v>
+        <v>-217.90783944888574</v>
       </c>
       <c r="D69" s="0">
-        <v>592.85198490449966</v>
+        <v>-222.05683257629397</v>
       </c>
       <c r="E69" s="0">
-        <v>586.75389730024608</v>
+        <v>-222.28889569261369</v>
       </c>
     </row>
     <row r="70">
@@ -1486,16 +1483,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>-130.75836923975888</v>
+        <v>41.755860869520959</v>
       </c>
       <c r="C70" s="0">
-        <v>-130.75616501644703</v>
+        <v>41.693852631205218</v>
       </c>
       <c r="D70" s="0">
-        <v>-133.11907107620033</v>
+        <v>39.709093024616791</v>
       </c>
       <c r="E70" s="0">
-        <v>-133.1396310277681</v>
+        <v>39.653582539809818</v>
       </c>
     </row>
     <row r="71">
@@ -1503,16 +1500,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>52.698969449979671</v>
+        <v>658.92742425464996</v>
       </c>
       <c r="C71" s="0">
-        <v>52.799784135295269</v>
+        <v>656.11670926875524</v>
       </c>
       <c r="D71" s="0">
-        <v>58.41450211730961</v>
+        <v>608.47748300533249</v>
       </c>
       <c r="E71" s="0">
-        <v>58.531295830945673</v>
+        <v>605.93522154306515</v>
       </c>
     </row>
     <row r="72">
@@ -1520,16 +1517,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>620.90681530661152</v>
+        <v>0.88354642704923714</v>
       </c>
       <c r="C72" s="0">
-        <v>618.6407407696372</v>
+        <v>0.88241916309224033</v>
       </c>
       <c r="D72" s="0">
-        <v>652.12724068341504</v>
+        <v>0.78227239575903029</v>
       </c>
       <c r="E72" s="0">
-        <v>644.06306358529241</v>
+        <v>0.78102198787841703</v>
       </c>
     </row>
     <row r="73">
@@ -1537,16 +1534,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>0.74283568028955094</v>
+        <v>0.83402841534261063</v>
       </c>
       <c r="C73" s="0">
-        <v>0.74491110342324462</v>
+        <v>0.83256929332087692</v>
       </c>
       <c r="D73" s="0">
-        <v>0.90910476962011855</v>
+        <v>0.78295777917683929</v>
       </c>
       <c r="E73" s="0">
-        <v>0.91101932477539604</v>
+        <v>0.78138724624792888</v>
       </c>
     </row>
     <row r="74">
@@ -1554,16 +1551,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>0.83276452357812925</v>
+        <v>0.3164371149960572</v>
       </c>
       <c r="C74" s="0">
-        <v>0.83387577094342669</v>
+        <v>0.31483514956423503</v>
       </c>
       <c r="D74" s="0">
-        <v>0.93250166550316405</v>
+        <v>0.30161416944269864</v>
       </c>
       <c r="E74" s="0">
-        <v>0.93348743944417689</v>
+        <v>0.29999072422279982</v>
       </c>
     </row>
     <row r="75">
@@ -1571,32 +1568,15 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>0.52881907522851213</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>0.52892949671178469</v>
+        <v>0</v>
       </c>
       <c r="D75" s="0">
-        <v>0.54941223370019865</v>
+        <v>0</v>
       </c>
       <c r="E75" s="0">
-        <v>0.54949894839766023</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76" s="0">
-        <v>0</v>
-      </c>
-      <c r="C76" s="0">
-        <v>0</v>
-      </c>
-      <c r="D76" s="0">
-        <v>0</v>
-      </c>
-      <c r="E76" s="0">
         <v>0</v>
       </c>
     </row>
